--- a/tests/testdata/excel/ファイル名/ﾊﾝｶｸｶﾅ.xlsx
+++ b/tests/testdata/excel/ファイル名/ﾊﾝｶｸｶﾅ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC3B0D6D-FC15-4BBD-BE0C-B815225E3C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DA08293-6456-4C48-9BEC-7AAD25976103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{6AC48754-49DA-4C7C-B9E6-B61D614D0D9B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{9EA24DD8-B769-4A4D-8756-84146907B3BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9634C7A-0CCD-492D-9670-C05CA88CCCC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C723E88C-9338-4064-A3F2-096C3B2248A7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/ﾊﾝｶｸｶﾅ.xlsx
+++ b/tests/testdata/excel/ファイル名/ﾊﾝｶｸｶﾅ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DA08293-6456-4C48-9BEC-7AAD25976103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DA2F17B-072E-4270-B758-785CBC7F8E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{9EA24DD8-B769-4A4D-8756-84146907B3BE}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{FB794156-AED9-4C6A-AB69-2D4ED091082E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C723E88C-9338-4064-A3F2-096C3B2248A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF82DE66-CFEC-48F4-A9C7-708096AB1EF9}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
